--- a/data/trans_dic/IP24_R_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,05; 26,34</t>
+          <t>11,81; 24,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,87; 21,51</t>
+          <t>9,62; 21,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,16; 21,02</t>
+          <t>12,41; 21,23</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 12,86</t>
+          <t>8,08; 20,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,01; 20,28</t>
+          <t>4,58; 12,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,41; 14,9</t>
+          <t>7,17; 14,66</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 16,37</t>
+          <t>6,74; 22,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,52; 19,45</t>
+          <t>3,62; 16,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 15,88</t>
+          <t>6,62; 16,77</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,9</t>
+          <t>9,58; 18,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,57; 18,2</t>
+          <t>4,93; 10,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,83; 12,34</t>
+          <t>8,24; 13,53</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 12,46</t>
+          <t>5,86; 16,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 16,11</t>
+          <t>4,08; 12,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,89; 12,66</t>
+          <t>6,43; 13,21</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 12,1</t>
+          <t>5,97; 20,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,3; 19,94</t>
+          <t>2,7; 12,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,1; 13,71</t>
+          <t>5,31; 13,74</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,67</t>
+          <t>11,16; 15,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,37; 14,95</t>
+          <t>7,09; 10,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,21; 12,24</t>
+          <t>9,79; 12,88</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>21171</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>36444</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11541; 27515</t>
+          <t>14440; 29566</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14839; 29366</t>
+          <t>9902; 22603</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29303; 50658</t>
+          <t>27951; 47799</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>12119</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20195</t>
+          <t>19688</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4095; 12106</t>
+          <t>7354; 18534</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7609; 19272</t>
+          <t>4397; 12130</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14013; 28191</t>
+          <t>13410; 27417</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11977</t>
+          <t>12178</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2210; 8492</t>
+          <t>3796; 12945</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3483; 12268</t>
+          <t>1937; 8791</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7374; 18259</t>
+          <t>7265; 18411</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>26714</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>28765</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>40041</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6869; 19320</t>
+          <t>19169; 36875</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20672; 39318</t>
+          <t>8778; 18785</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29563; 53442</t>
+          <t>31153; 51164</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>15516</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23997</t>
+          <t>24829</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4801; 14878</t>
+          <t>8664; 25015</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9441; 26140</t>
+          <t>4846; 15354</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16595; 35651</t>
+          <t>17142; 35239</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>7968</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12077</t>
+          <t>12310</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1703; 8336</t>
+          <t>4079; 13880</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3820; 14357</t>
+          <t>1899; 8488</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7187; 19318</t>
+          <t>7357; 19057</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>88</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>55430</t>
+          <t>90883</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>92934</t>
+          <t>54607</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>148364</t>
+          <t>145490</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>44346; 69945</t>
+          <t>76564; 108486</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>77270; 111343</t>
+          <t>43942; 65641</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>129066; 171516</t>
+          <t>127852; 168070</t>
         </is>
       </c>
     </row>
